--- a/ig/main/ValueSet-JDV-J60-FormatCode-DMP.xlsx
+++ b/ig/main/ValueSet-JDV-J60-FormatCode-DMP.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20240223120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/ValueSet-JDV-J60-FormatCode-DMP.xlsx
+++ b/ig/main/ValueSet-JDV-J60-FormatCode-DMP.xlsx
@@ -84,7 +84,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/ValueSet-JDV-J60-FormatCode-DMP.xlsx
+++ b/ig/main/ValueSet-JDV-J60-FormatCode-DMP.xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_A06_FormatCo" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE_A11_IheForma" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE_A09_DICOMuid" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from TRE_A10_Nomencla" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>

--- a/ig/main/ValueSet-JDV-J60-FormatCode-DMP.xlsx
+++ b/ig/main/ValueSet-JDV-J60-FormatCode-DMP.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="158">
   <si>
     <t>Property</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240223120000</t>
+    <t>20240927120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T12:00:00+01:00</t>
+    <t>2024-09-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -186,24 +186,6 @@
     <t>Document de liaison d'urgence</t>
   </si>
   <si>
-    <t>urn:asip:ci-sis:dlu-dlu-dom:2022</t>
-  </si>
-  <si>
-    <t>Document de liaison d'urgence DOM</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:dlu-fludr-dom:2022</t>
-  </si>
-  <si>
-    <t>Fiche de liaison d'urgence - Retour des urgences vers le domicile</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:dlu-fludt-dom:2022</t>
-  </si>
-  <si>
-    <t>Fiche de liaison d'urgence - Transfert du domicile vers les urgences</t>
-  </si>
-  <si>
     <t>urn:ans:ci-sis:cse-mde:2023</t>
   </si>
   <si>
@@ -384,6 +366,27 @@
     <t>Plan personnalisé de prévention</t>
   </si>
   <si>
+    <t>urn:asip:ci-sis:dlu:2024</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ft-su:2024</t>
+  </si>
+  <si>
+    <t>Fiche de transfert vers le service des urgences</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:fr-su:2024</t>
+  </si>
+  <si>
+    <t>Fiche de retour du service des urgences</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:trod:2024</t>
+  </si>
+  <si>
+    <t>Test rapide d'orientation diagnostique</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -448,9 +451,6 @@
   </si>
   <si>
     <t>urn:ihe:pcc:ips:2020</t>
-  </si>
-  <si>
-    <t>Synthèse du dossier médical</t>
   </si>
   <si>
     <t>urn:ihe:pharm:pre:2010</t>
@@ -759,7 +759,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1123,28 +1123,28 @@
         <v>116</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>117</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>119</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>121</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>122</v>
@@ -1155,7 +1155,15 @@
         <v>123</v>
       </c>
       <c r="B49" t="s" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
         <v>124</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1182,82 +1190,82 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -1286,15 +1294,15 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>151</v>
@@ -1332,15 +1340,15 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>154</v>
@@ -1378,15 +1386,15 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>157</v>
